--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.136.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.136.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.136.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.136.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -597,16 +597,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L20: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Â£â€”, and any costs justly payable to hi</t>
+          <t>L4: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: ed ； and</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L28: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: The above follows the English form No. 7.â€˜</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]ORDERS OF JANUARY 1851.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]ORDERS OF JANUARY 1851.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L35: isolated marker/symbol line :: 129</t>
@@ -624,7 +628,7 @@
       </c>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L8: punctuation artifact: double/multiple hyphen :: upon the said mortgage (or lien) is the sum of Â£--,or</t>
+          <t>L8: punctuation artifact: double/multiple hyphen :: upon the said mortgage (or lien) is the sum of £--,or</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
@@ -653,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>94</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -664,19 +668,19 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L29: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: or lien) is the sum of Â£â€”, or</t>
+          <t>L71: stray/suspicious non-ASCII glyph(s): U+FF09 FULLWIDTH RIGHT PARENTHESIS | isolated marker/symbol line :: ）</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN | isolated marker/symbol line :: â‚¬</t>
+          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: €</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L81: isolated marker/symbol line :: G</t>
+          <t>L71: stray/suspicious non-ASCII glyph(s): U+FF09 FULLWIDTH RIGHT PARENTHESIS | isolated marker/symbol line :: ）</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
@@ -691,7 +695,7 @@
       </c>
       <c r="Q3" s="1" t="inlineStr">
         <is>
-          <t>L12: punctuation artifact: double/multiple hyphen :: Â£-----, and any costs justly payable to him, and to recon-</t>
+          <t>L12: punctuation artifact: double/multiple hyphen :: £-----, and any costs justly payable to him, and to recon-</t>
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
@@ -725,26 +729,18 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: relief ; pray subpÃ¦na.)</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L92: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” day of</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L100: isolated marker/symbol line :: -</t>
+          <t>L81: isolated marker/symbol line :: G</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN | isolated marker/symbol line :: â‚¬</t>
+          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: €</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -770,12 +766,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -784,17 +780,13 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L99: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of â€”-</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L101: isolated marker/symbol line | punctuation artifact: double/multiple hyphen :: --</t>
+          <t>L100: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -841,7 +833,7 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L121: symbol-only separator/garbage line :: 1.1</t>
+          <t>L101: isolated marker/symbol line | punctuation artifact: double/multiple hyphen :: --</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
@@ -888,7 +880,7 @@
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L122: isolated marker/symbol line :: T</t>
+          <t>L121: symbol-only separator/garbage line :: 1.1</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
@@ -933,7 +925,11 @@
       <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
-      <c r="N8" s="1" t="inlineStr"/>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>L122: isolated marker/symbol line :: T</t>
+        </is>
+      </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
           <t>L116: isolated marker/symbol line :: 11</t>
@@ -1001,12 +997,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1049,7 +1045,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1083,7 +1079,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
